--- a/templates/docs/M-02.xlsx
+++ b/templates/docs/M-02.xlsx
@@ -1554,8 +1554,16 @@
           <t>供應商資訊安全管理程序</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -1567,11 +1575,15 @@
           <t>A.5.19、A.5.20、A.5.21、A.5.22、A.5.23</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr"/>
@@ -1592,8 +1604,16 @@
           <t>變更與組態管理程序</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -1609,11 +1629,15 @@
           <t>A.8.9、A.8.32</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
@@ -1634,8 +1658,16 @@
           <t>實體與環境安全管理辦法</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -1647,11 +1679,15 @@
           <t>A.7.1、A.7.2、A.7.4、A.7.11</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
@@ -1672,8 +1708,16 @@
           <t>帳號與權限清冊維護作業指引</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -1685,11 +1729,15 @@
           <t>A.5.16、A.5.18、A.5.37</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
@@ -2022,8 +2070,16 @@
           <t>變更申請單</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -2039,11 +2095,15 @@
           <t>A.8.32</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
@@ -2334,8 +2394,16 @@
           <t>營運衝擊分析（BIA）</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>【YYYY/MM/DD】</t>
+        </is>
+      </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
           <t>【制定單位】</t>
@@ -2347,11 +2415,15 @@
           <t>A.5.30</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>【存放路徑】</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>草案</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
